--- a/data/trans_orig/P37C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Provincia-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023</t>
+          <t>Población según la creencia de si es importante vacunar a los niños/as en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,82 +730,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1798</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4405</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>919</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4619</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>919</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>2667</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>7014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>548</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5614</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17475</t>
+          <t>16295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5713</t>
+          <t>5697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>21701</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9772</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21345</t>
+          <t>21252</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>17688</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37165</t>
+          <t>36154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278439</t>
+          <t>278406</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298052</t>
+          <t>298081</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264251</t>
+          <t>264812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277108</t>
+          <t>277539</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,47 +1232,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>95,82%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>562508</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>549525</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>572857</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>93,94%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>91,77%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>95,67%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>562508</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>548959</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>572064</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>91,68%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>524</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>8602</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2600</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9438</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13646</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34422</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11377</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29692</t>
+          <t>28813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>54317</t>
+          <t>53541</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144899</t>
+          <t>143653</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199377</t>
+          <t>199893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>126078</t>
+          <t>123469</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>162585</t>
+          <t>161754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>276430</t>
+          <t>285256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348172</t>
+          <t>353052</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>292328</t>
+          <t>293079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348453</t>
+          <t>349128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>327035</t>
+          <t>328448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364782</t>
+          <t>366564</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>635900</t>
+          <t>634513</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>706912</t>
+          <t>702532</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -2207,97 +2207,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1268</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1679</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4010</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>1268</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4442</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>4469</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1268</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>3897</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>16931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12200</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>33525</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9525</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>26302</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267570</t>
+          <t>268789</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>291556</t>
+          <t>290825</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>309608</t>
+          <t>308983</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325714</t>
+          <t>325620</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>585093</t>
+          <t>583725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613180</t>
+          <t>611745</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -2776,82 +2776,82 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>404</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3076</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1930</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2889,97 +2889,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1528</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22639</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34622</t>
+          <t>32943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>899</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6519</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1591</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7437</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276540</t>
+          <t>279531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>297742</t>
+          <t>298236</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>444846</t>
+          <t>448009</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>467369</t>
+          <t>467128</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>737034</t>
+          <t>737534</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762948</t>
+          <t>762914</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3458,97 +3458,97 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>592</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>10899</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14480</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6594</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>19283</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94205</t>
+          <t>94545</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>117347</t>
+          <t>115675</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144757</t>
+          <t>144048</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>162486</t>
+          <t>161958</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>245513</t>
+          <t>243926</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>273858</t>
+          <t>273068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,08%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>48044</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>70538</t>
+          <t>69647</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>40190</t>
+          <t>41208</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>58287</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94764</t>
+          <t>94687</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122183</t>
+          <t>121918</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16269</t>
+          <t>16468</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3961</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17331</t>
+          <t>17348</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9007</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2950</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7289</t>
+          <t>7126</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20452</t>
+          <t>20556</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13020</t>
+          <t>13436</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>29173</t>
+          <t>30258</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27676</t>
+          <t>27541</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>49769</t>
+          <t>48464</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19085</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34444</t>
+          <t>36421</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79437</t>
+          <t>79150</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>194526</t>
+          <t>195595</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>221503</t>
+          <t>220911</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>210279</t>
+          <t>209451</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>227798</t>
+          <t>227485</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>410556</t>
+          <t>412309</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>442710</t>
+          <t>443397</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8672</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1188</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14312</t>
+          <t>14094</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>13345</t>
+          <t>12581</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1228</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19100</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>16416</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37979</t>
+          <t>37819</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10168</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>39091</t>
+          <t>38596</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>29779</t>
+          <t>28295</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>66176</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>119172</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>168475</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>50321</t>
+          <t>52091</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>165391</t>
+          <t>165891</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>165816</t>
+          <t>155832</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>313479</t>
+          <t>316415</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>414829</t>
+          <t>414880</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>467564</t>
+          <t>466797</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>634212</t>
+          <t>635841</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>775131</t>
+          <t>772899</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1071532</t>
+          <t>1070387</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1257270</t>
+          <t>1265293</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,47%</t>
         </is>
       </c>
     </row>
@@ -5504,82 +5504,82 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>2337</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3665</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="R46" s="2" t="inlineStr">
         <is>
           <t>595</t>
         </is>
       </c>
-      <c r="L46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M46" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>595</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>20060</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5632,12 +5632,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>1139</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7537</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>22028</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5730,12 +5730,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>17411</t>
+          <t>20259</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>64700</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5745,12 +5745,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>16041</t>
+          <t>14594</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>32433</t>
+          <t>31736</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>39616</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>83884</t>
+          <t>84016</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -5843,12 +5843,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>91226</t>
+          <t>88471</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>289584</t>
+          <t>291924</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5858,12 +5858,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>168855</t>
+          <t>166994</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>209506</t>
+          <t>210425</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>245036</t>
+          <t>236205</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>475822</t>
+          <t>475608</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>567465</t>
+          <t>563807</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>813185</t>
+          <t>816855</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>478460</t>
+          <t>478482</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>522278</t>
+          <t>522479</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1074401</t>
+          <t>1074331</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1357800</t>
+          <t>1357743</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6041,12 +6041,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6186</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22763</t>
+          <t>22590</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>19711</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>14437</t>
+          <t>14380</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>35446</t>
+          <t>37280</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>37094</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9469</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>25680</t>
+          <t>24609</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>31925</t>
+          <t>31098</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>104141</t>
+          <t>102506</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>163464</t>
+          <t>162526</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>73394</t>
+          <t>73397</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>114404</t>
+          <t>115476</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>190048</t>
+          <t>189601</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>260180</t>
+          <t>262299</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>569776</t>
+          <t>550491</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>768826</t>
+          <t>771707</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>533214</t>
+          <t>540784</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>722385</t>
+          <t>729519</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1180851</t>
+          <t>1176479</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1467430</t>
+          <t>1470616</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2481958</t>
+          <t>2474193</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2732579</t>
+          <t>2750697</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2792575</t>
+          <t>2786360</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3003513</t>
+          <t>3005311</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5306822</t>
+          <t>5298955</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5646835</t>
+          <t>5645567</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37C1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37C1_2023-Provincia-trans_orig.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4405</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>5625</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2203</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5697</t>
+          <t>5632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>14856</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>10218</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21252</t>
+          <t>21065</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25741</t>
+          <t>25496</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>18284</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36154</t>
+          <t>35459</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>290719</t>
+          <t>298222</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278406</t>
+          <t>289314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>298081</t>
+          <t>305385</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>271789</t>
+          <t>297318</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>264812</t>
+          <t>289849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277539</t>
+          <t>303018</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>562508</t>
+          <t>595539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>549525</t>
+          <t>583173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>572857</t>
+          <t>604986</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,57%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>309160</t>
+          <t>316942</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>309160</t>
+          <t>316942</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>309160</t>
+          <t>316942</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>598795</t>
+          <t>633002</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>598795</t>
+          <t>633002</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>598795</t>
+          <t>633002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5016</t>
+          <t>4135</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2720</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>7938</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2778</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>8602</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,05%</t>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>7916</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22535</t>
+          <t>22708</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>34652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>25777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>39692</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28813</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53541</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>171371</t>
+          <t>176614</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143653</t>
+          <t>150491</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199893</t>
+          <t>206183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>142937</t>
+          <t>151911</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>123469</t>
+          <t>132725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>161754</t>
+          <t>170570</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>314308</t>
+          <t>328524</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>285256</t>
+          <t>295486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353052</t>
+          <t>360262</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,55%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>321991</t>
+          <t>328914</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>293079</t>
+          <t>300336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356139</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>347787</t>
+          <t>368709</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>328448</t>
+          <t>349357</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>366564</t>
+          <t>387315</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>67,79%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,45%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>669778</t>
+          <t>697622</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>634513</t>
+          <t>662731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>702532</t>
+          <t>731244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513006</t>
+          <t>544015</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1030399</t>
+          <t>1073674</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1838</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6670</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>4200</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>8575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15948</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>20580</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12200</t>
+          <t>13781</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>28880</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9599</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22419</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>36957</t>
+          <t>37184</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26302</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>49942</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>281069</t>
+          <t>279856</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268789</t>
+          <t>267002</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290825</t>
+          <t>290277</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>318325</t>
+          <t>326913</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>308983</t>
+          <t>317467</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325620</t>
+          <t>334485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>599394</t>
+          <t>606769</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>583725</t>
+          <t>592686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>611745</t>
+          <t>621023</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,85%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>314183</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>314183</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>314094</t>
+          <t>314183</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>345342</t>
+          <t>354698</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>345342</t>
+          <t>354698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>345342</t>
+          <t>354698</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>659436</t>
+          <t>668881</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>659436</t>
+          <t>668881</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>659436</t>
+          <t>668881</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2816,12 +2816,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>431</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9686</t>
+          <t>18998</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6629</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21222</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>27916</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32943</t>
+          <t>48559</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>587</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,92 +3120,92 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>6822</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7199</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>1067</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>6821</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>3533</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>1336</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>292124</t>
+          <t>335751</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>279531</t>
+          <t>315879</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>298236</t>
+          <t>344806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>461855</t>
+          <t>405548</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>448009</t>
+          <t>392222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>467128</t>
+          <t>411346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>753980</t>
+          <t>741299</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>737534</t>
+          <t>719991</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>762914</t>
+          <t>752422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>302391</t>
+          <t>355336</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>471840</t>
+          <t>417999</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>774232</t>
+          <t>773335</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>4096</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2643</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>10899</t>
+          <t>12145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>10348</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14480</t>
+          <t>18342</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3312</t>
+          <t>3814</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>7593</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>19283</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>105561</t>
+          <t>121663</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>94545</t>
+          <t>107946</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>132349</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>153675</t>
+          <t>166881</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>144048</t>
+          <t>156460</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>161958</t>
+          <t>175569</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>259236</t>
+          <t>288544</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>243926</t>
+          <t>272238</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>273068</t>
+          <t>303679</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>59374</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>57402</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>48790</t>
+          <t>53054</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>41208</t>
+          <t>44763</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58287</t>
+          <t>62894</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>108164</t>
+          <t>120174</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94687</t>
+          <t>105128</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>121918</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>176288</t>
+          <t>203226</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>226392</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>384150</t>
+          <t>429618</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>16468</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4112</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>845</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>3308</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>12307</t>
+          <t>13253</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20556</t>
+          <t>20356</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>14417</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>19532</t>
+          <t>21296</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>30258</t>
+          <t>30054</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>37022</t>
+          <t>39230</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>27541</t>
+          <t>29050</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>48464</t>
+          <t>51014</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>21154</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>36421</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>64254</t>
+          <t>67830</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>51634</t>
+          <t>54652</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>79150</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>209692</t>
+          <t>208459</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>195595</t>
+          <t>195581</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>220911</t>
+          <t>221473</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>219239</t>
+          <t>223746</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>209451</t>
+          <t>212955</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>227485</t>
+          <t>232056</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>428931</t>
+          <t>432205</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>412309</t>
+          <t>416576</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>443397</t>
+          <t>448550</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>255579</t>
+          <t>262304</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>525215</t>
+          <t>533011</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>5481</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>2362</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>7939</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3109</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17103</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>5983</t>
+          <t>8423</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>12581</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1544</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>10420</t>
+          <t>13038</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>31818</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>19698</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>37819</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>23309</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>38596</t>
+          <t>39876</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>48245</t>
+          <t>58641</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>28295</t>
+          <t>41953</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>66176</t>
+          <t>77550</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>141282</t>
+          <t>167574</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>119172</t>
+          <t>139055</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>195989</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>120081</t>
+          <t>147243</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>52091</t>
+          <t>129033</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>165891</t>
+          <t>169768</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>261363</t>
+          <t>314818</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>155832</t>
+          <t>283360</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>316415</t>
+          <t>346624</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>442235</t>
+          <t>500169</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>414880</t>
+          <t>470164</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>466797</t>
+          <t>527244</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>693005</t>
+          <t>583888</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>635841</t>
+          <t>561279</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>772899</t>
+          <t>606017</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1135241</t>
+          <t>1084058</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1070387</t>
+          <t>1045583</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1265293</t>
+          <t>1117288</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>75,53%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>616894</t>
+          <t>710538</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>616894</t>
+          <t>710538</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>616894</t>
+          <t>710538</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>846313</t>
+          <t>768773</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>846313</t>
+          <t>768773</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>846313</t>
+          <t>768773</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1463208</t>
+          <t>1479312</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1463208</t>
+          <t>1479312</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1463208</t>
+          <t>1479312</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>688</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>10950</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,22 +5647,22 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1139</t>
+          <t>1327</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>23808</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -5725,69 +5725,69 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>42305</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>38774</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>64700</t>
+          <t>71515</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>4,86%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>27402</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>19077</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>37912</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
           <t>4,56%</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,18%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>22388</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>14594</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr">
-        <is>
-          <t>31736</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="P48" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
           <t>81</t>
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>64693</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>39616</t>
+          <t>64092</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>84016</t>
+          <t>100391</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -5838,32 +5838,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>206466</t>
+          <t>241046</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>214797</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>291924</t>
+          <t>270779</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,32 +5873,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>188164</t>
+          <t>214650</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>166994</t>
+          <t>190461</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>210425</t>
+          <t>238262</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>394630</t>
+          <t>455696</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>236205</t>
+          <t>419170</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>475608</t>
+          <t>488692</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -5951,32 +5951,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>668999</t>
+          <t>491426</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>563807</t>
+          <t>462360</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>816855</t>
+          <t>518450</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5986,32 +5986,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>500995</t>
+          <t>584201</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>478482</t>
+          <t>560313</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>522479</t>
+          <t>609562</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,46%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,32 +6021,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>1169994</t>
+          <t>1075627</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1074331</t>
+          <t>1038812</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>1357743</t>
+          <t>1113298</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>715392</t>
+          <t>830609</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1644112</t>
+          <t>1628681</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5795</t>
+          <t>5526</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22590</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>6758</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,17 +6251,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>23294</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>14380</t>
+          <t>14796</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>37280</t>
+          <t>36325</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>20823</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>16202</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>26524</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>42331</t>
+          <t>47884</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>31098</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>56548</t>
+          <t>65639</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>133877</t>
+          <t>166341</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>102506</t>
+          <t>141103</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>162526</t>
+          <t>201062</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>92033</t>
+          <t>106602</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>73397</t>
+          <t>89719</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>115476</t>
+          <t>128026</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>225909</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>189601</t>
+          <t>237894</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>262299</t>
+          <t>307347</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>696038</t>
+          <t>780317</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>550491</t>
+          <t>724238</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>771707</t>
+          <t>836341</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,32 +6555,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>663984</t>
+          <t>741464</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>540784</t>
+          <t>698674</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>729519</t>
+          <t>783147</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1360022</t>
+          <t>1521781</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1176479</t>
+          <t>1453889</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>1470616</t>
+          <t>1590458</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2566204</t>
+          <t>2509916</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2474193</t>
+          <t>2449736</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2750697</t>
+          <t>2571303</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>2861786</t>
+          <t>2843378</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2786360</t>
+          <t>2799457</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3005311</t>
+          <t>2889756</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>75,24%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>5427989</t>
+          <t>5353294</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>5298955</t>
+          <t>5281697</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5645567</t>
+          <t>5424714</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3434578</t>
+          <t>3498664</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3644969</t>
+          <t>3720850</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7079546</t>
+          <t>7219514</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
